--- a/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
+++ b/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="360">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -41,28 +41,28 @@
     <t xml:space="preserve">Number Cohort</t>
   </si>
   <si>
-    <t xml:space="preserve">48 (21.72%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173 (78.28%)</t>
+    <t xml:space="preserve">45 (20.36%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176 (79.64%)</t>
   </si>
   <si>
     <t xml:space="preserve">Female</t>
   </si>
   <si>
-    <t xml:space="preserve">27 (56.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75 (43.4%)</t>
+    <t xml:space="preserve">25 (55.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77 (43.8%)</t>
   </si>
   <si>
     <t xml:space="preserve">Male</t>
   </si>
   <si>
-    <t xml:space="preserve">21 (43.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98 (56.6%)</t>
+    <t xml:space="preserve">20 (44.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99 (56.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">American Indian or Alaska Native</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">0 (0%)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 (1.2%)</t>
+    <t xml:space="preserve">2 (1.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">Asian</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">Black or African American</t>
   </si>
   <si>
-    <t xml:space="preserve">5 (10.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (8.1%)</t>
+    <t xml:space="preserve">5 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (8%)</t>
   </si>
   <si>
     <t xml:space="preserve">More Than One Race</t>
@@ -98,52 +98,55 @@
     <t xml:space="preserve">Other/Unknown Race</t>
   </si>
   <si>
-    <t xml:space="preserve">8 (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (11.6%)</t>
+    <t xml:space="preserve">7 (15.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 (11.9%)</t>
   </si>
   <si>
     <t xml:space="preserve">White</t>
   </si>
   <si>
-    <t xml:space="preserve">35 (72.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133 (76.9%)</t>
+    <t xml:space="preserve">33 (73.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135 (76.7%)</t>
   </si>
   <si>
     <t xml:space="preserve">Hispanic or Latino</t>
   </si>
   <si>
+    <t xml:space="preserve">4 (8.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (8.5%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not Hispanic or Latino</t>
   </si>
   <si>
-    <t xml:space="preserve">41 (85.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158 (91.3%)</t>
+    <t xml:space="preserve">39 (86.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 (90.9%)</t>
   </si>
   <si>
     <t xml:space="preserve">Other/Unknown Ethnicity</t>
   </si>
   <si>
-    <t xml:space="preserve">2 (4.2%)</t>
+    <t xml:space="preserve">2 (4.4%)</t>
   </si>
   <si>
     <t xml:space="preserve">AFR</t>
   </si>
   <si>
-    <t xml:space="preserve">4 (8.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (9.8%)</t>
+    <t xml:space="preserve">17 (9.7%)</t>
   </si>
   <si>
     <t xml:space="preserve">AMR</t>
   </si>
   <si>
-    <t xml:space="preserve">7 (14.6%)</t>
+    <t xml:space="preserve">16 (9.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">EAS</t>
@@ -152,723 +155,729 @@
     <t xml:space="preserve">EUR</t>
   </si>
   <si>
-    <t xml:space="preserve">36 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135 (78%)</t>
+    <t xml:space="preserve">35 (77.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136 (77.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">SAS</t>
   </si>
   <si>
+    <t xml:space="preserve">1 (2.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (2.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_os_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_efs_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_tmb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 (28.12%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69 (71.88%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (44.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 (36.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (55.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 (63.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (1.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (3.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (2.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (8.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (11.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (74.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 (72.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (7.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 (85.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61 (88.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (4.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (13%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (5.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 (69.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (13.92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68 (86.08%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (9.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (90.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (4.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (8.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (1.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (81.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 (73.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63 (92.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (18.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (7.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (72.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56 (82.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (15.49%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 (84.51%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (45.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 (41.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (54.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 (58.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (6.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (18.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41 (68.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (13.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 (81.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (15%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (8.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 (70%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 (34.21%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 (65.79%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (46.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 (52%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (3.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (14%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA (NA%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (30.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (57.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39 (78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (23.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 (69.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 (84%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (7.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (26.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 (44%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;NA&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (15.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (48%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (10.26%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 (89.74%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (42.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (57.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (11.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 (71.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (8.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 (91.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (68.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (29.63%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (70.37%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (52.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (47.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (12.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (31.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (5.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (37.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (10.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (89.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (36.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (15.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (68%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (29.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (70.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (23.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (5.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (52.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (87.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (88.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (58.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (11.32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 (88.68%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 (61.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (31.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (6.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (12.8%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 (2.1%)</t>
   </si>
   <si>
-    <t xml:space="preserve">4 (2.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_os_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_efs_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_tmb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32</t>
+    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (66.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 (48.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (16.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (21.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 (59.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (19.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (23.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (83.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 (38.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (4.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (25.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (26.32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (73.68%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (35.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (40%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (64.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (28.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (80%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (71.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (7.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (21.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (92.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (73.33%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (26.67%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (36.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73</t>
   </si>
   <si>
     <t xml:space="preserve">0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">28 (29.17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68 (70.83%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (42.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 (36.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (57.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 (63.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (1.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (3.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (2.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (8.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (11.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49 (72.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (7.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (85.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 (88.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (4.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (13.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (5.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 (69.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (13.92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68 (86.08%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (9.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (90.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (81.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 (73.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63 (92.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (18.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (72.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56 (82.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (18.31%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58 (81.69%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (46.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (41.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (53.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34 (58.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (6.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (7.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (92.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39 (67.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (13.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 (81%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (5.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (15.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (8.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40 (69%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 (35.53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49 (64.47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (48.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 (51%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (34.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (3.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (4.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA (NA%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (29.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (59.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38 (77.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (22.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (8.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (70.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41 (83.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (7.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (25.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 (44.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;NA&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (18.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (46.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (10.26%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 (89.74%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (42.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (57.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (11.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 (71.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (8.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 (91.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (68.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (29.63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (70.37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (52.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (47.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (12.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (31.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (5.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (37.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (10.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (89.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (36.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (15.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (29.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (70.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (23.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (5.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (17.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (52.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (11.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (87.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (88.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (58.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (11.32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 (88.68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 (61.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (31.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (6.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (12.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (33.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (66.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (48.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (21.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 (59.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (19.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (23.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (83.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 (38.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (4.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (25.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (26.32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (73.68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (35.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (64.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (28.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (71.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (7.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (21.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (92.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (73.33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (26.67%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (45.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (54.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (36.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.11</t>
   </si>
   <si>
@@ -977,25 +986,49 @@
     <t xml:space="preserve">0.81</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (44.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (77.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51</t>
+    <t xml:space="preserve">3 (23.08%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (76.92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (70%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (80%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97</t>
   </si>
   <si>
     <t xml:space="preserve">0.22</t>
@@ -1517,29 +1550,29 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -1547,29 +1580,29 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1580,68 +1613,68 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1671,10 +1704,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
@@ -1682,10 +1715,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4">
@@ -1693,10 +1726,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -1704,10 +1737,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
@@ -1715,10 +1748,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7">
@@ -1729,117 +1762,117 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1869,10 +1902,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -1880,10 +1913,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4">
@@ -1891,10 +1924,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
@@ -1902,10 +1935,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
@@ -1913,10 +1946,10 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -1924,10 +1957,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8">
@@ -1938,106 +1971,106 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>282</v>
       </c>
       <c r="C17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -2067,10 +2100,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -2078,10 +2111,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4">
@@ -2089,10 +2122,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5">
@@ -2103,7 +2136,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6">
@@ -2114,7 +2147,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7">
@@ -2122,10 +2155,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
@@ -2136,106 +2169,106 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C14" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C16" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2265,10 +2298,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -2276,10 +2309,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -2287,10 +2320,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -2301,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6">
@@ -2312,7 +2345,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7">
@@ -2320,10 +2353,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8">
@@ -2334,95 +2367,95 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C13" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C15" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C16" t="s">
-        <v>316</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2452,10 +2485,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3">
@@ -2463,10 +2496,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4">
@@ -2474,10 +2507,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5">
@@ -2488,7 +2521,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6">
@@ -2499,7 +2532,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7">
@@ -2507,10 +2540,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C7" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8">
@@ -2521,106 +2554,106 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C9" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C13" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C14" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -2650,10 +2683,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3">
@@ -2661,10 +2694,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C3" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4">
@@ -2675,7 +2708,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5">
@@ -2686,7 +2719,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6">
@@ -2694,10 +2727,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7">
@@ -2708,95 +2741,95 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C8" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C11" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C12" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C13" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C14" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -2826,10 +2859,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3">
@@ -2837,10 +2870,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4">
@@ -2848,10 +2881,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
@@ -2862,7 +2895,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
@@ -2873,7 +2906,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
@@ -2881,10 +2914,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -2892,10 +2925,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2903,120 +2936,120 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C14" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="C16" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C17" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C18" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>282</v>
       </c>
       <c r="C19" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3046,10 +3079,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -3057,10 +3090,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
@@ -3068,10 +3101,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -3082,7 +3115,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -3090,10 +3123,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -3101,10 +3134,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -3112,10 +3145,10 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -3123,10 +3156,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -3134,10 +3167,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -3145,131 +3178,131 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3299,10 +3332,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -3310,10 +3343,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -3321,10 +3354,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
         <v>91</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -3335,7 +3368,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -3346,7 +3379,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -3354,10 +3387,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -3368,7 +3401,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -3376,10 +3409,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -3387,10 +3420,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -3401,128 +3434,128 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3552,10 +3585,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3">
@@ -3563,10 +3596,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
@@ -3574,10 +3607,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -3588,7 +3621,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6">
@@ -3599,7 +3632,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
@@ -3607,10 +3640,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8">
@@ -3618,10 +3651,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
@@ -3629,120 +3662,120 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3772,10 +3805,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
@@ -3783,10 +3816,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
@@ -3794,21 +3827,21 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
@@ -3816,10 +3849,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -3827,10 +3860,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8">
@@ -3838,10 +3871,10 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
@@ -3849,10 +3882,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
         <v>142</v>
-      </c>
-      <c r="C9" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -3860,10 +3893,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3871,131 +3904,131 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" t="s">
         <v>149</v>
-      </c>
-      <c r="C13" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4025,10 +4058,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -4036,10 +4069,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -4047,10 +4080,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5">
@@ -4061,7 +4094,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6">
@@ -4069,10 +4102,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
@@ -4083,7 +4116,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8">
@@ -4091,10 +4124,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9">
@@ -4102,109 +4135,109 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -4234,10 +4267,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3">
@@ -4245,10 +4278,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4">
@@ -4256,10 +4289,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5">
@@ -4267,10 +4300,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
@@ -4281,7 +4314,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
@@ -4289,10 +4322,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -4300,10 +4333,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9">
@@ -4311,109 +4344,109 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -4443,10 +4476,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
@@ -4454,10 +4487,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4">
@@ -4465,10 +4498,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
@@ -4479,7 +4512,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
@@ -4490,7 +4523,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
@@ -4498,10 +4531,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4542,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
@@ -4523,128 +4556,128 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -4674,10 +4707,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3">
@@ -4685,10 +4718,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
@@ -4696,21 +4729,21 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
@@ -4721,7 +4754,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7">
@@ -4732,18 +4765,18 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
@@ -4751,10 +4784,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -4762,10 +4795,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -4773,142 +4806,142 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C12" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C15" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C17" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C23" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
+++ b/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="358">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -443,66 +443,63 @@
     <t xml:space="preserve">26 (52%)</t>
   </si>
   <si>
+    <t xml:space="preserve">14 (53.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (48%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (3.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA (NA%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (30.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (14%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (57.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39 (78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (23.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 (69.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 (84%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (7.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (26.9%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">13 (50%)</t>
   </si>
   <si>
-    <t xml:space="preserve">17 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (3.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA (NA%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (30.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (57.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39 (78%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (23.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 (69.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 (84%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (7.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (26.9%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">22 (44%)</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;NA&gt;</t>
+    <t xml:space="preserve">Other/Unknown Ancestry</t>
   </si>
   <si>
     <t xml:space="preserve">4 (15.4%)</t>
   </si>
   <si>
-    <t xml:space="preserve">24 (48%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
@@ -719,58 +716,55 @@
     <t xml:space="preserve">29 (61.7%)</t>
   </si>
   <si>
-    <t xml:space="preserve">15 (31.9%)</t>
+    <t xml:space="preserve">18 (38.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (12.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (66.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 (48.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (16.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (21.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 (59.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (19.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (23.4%)</t>
   </si>
   <si>
     <t xml:space="preserve">3 (6.4%)</t>
   </si>
   <si>
-    <t xml:space="preserve">6 (12.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (33.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (66.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (48.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (21.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 (59.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (19.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (23.4%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 (83.3%)</t>
   </si>
   <si>
-    <t xml:space="preserve">18 (38.3%)</t>
+    <t xml:space="preserve">12 (25.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">2 (4.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (25.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">7.07</t>
@@ -1704,10 +1698,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -1715,10 +1709,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
@@ -1726,10 +1720,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
@@ -1737,10 +1731,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
@@ -1748,10 +1742,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
@@ -1762,7 +1756,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
@@ -1770,10 +1764,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9">
@@ -1784,7 +1778,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -1795,7 +1789,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
@@ -1803,10 +1797,10 @@
         <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -1814,10 +1808,10 @@
         <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13">
@@ -1825,10 +1819,10 @@
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1836,10 +1830,10 @@
         <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15">
@@ -1847,10 +1841,10 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16">
@@ -1858,7 +1852,7 @@
         <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -1869,7 +1863,7 @@
         <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C17" t="s">
         <v>132</v>
@@ -1902,10 +1896,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">
@@ -1916,7 +1910,7 @@
         <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4">
@@ -1927,7 +1921,7 @@
         <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -1935,10 +1929,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
@@ -1949,7 +1943,7 @@
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -1960,7 +1954,7 @@
         <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8">
@@ -1971,7 +1965,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
@@ -1982,7 +1976,7 @@
         <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -1993,7 +1987,7 @@
         <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -2001,10 +1995,10 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -2015,7 +2009,7 @@
         <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -2026,7 +2020,7 @@
         <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14">
@@ -2034,10 +2028,10 @@
         <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15">
@@ -2045,10 +2039,10 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16">
@@ -2056,10 +2050,10 @@
         <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C16" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17">
@@ -2067,10 +2061,10 @@
         <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -2100,10 +2094,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3">
@@ -2111,10 +2105,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4">
@@ -2122,10 +2116,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5">
@@ -2136,7 +2130,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
@@ -2147,7 +2141,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -2155,10 +2149,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8">
@@ -2169,7 +2163,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -2177,10 +2171,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -2191,7 +2185,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11">
@@ -2199,10 +2193,10 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12">
@@ -2213,7 +2207,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13">
@@ -2221,10 +2215,10 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -2232,10 +2226,10 @@
         <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15">
@@ -2243,10 +2237,10 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16">
@@ -2254,10 +2248,10 @@
         <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17">
@@ -2265,7 +2259,7 @@
         <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
         <v>110</v>
@@ -2298,10 +2292,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3">
@@ -2309,10 +2303,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4">
@@ -2320,10 +2314,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
@@ -2334,7 +2328,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6">
@@ -2345,7 +2339,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7">
@@ -2353,10 +2347,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8">
@@ -2367,7 +2361,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -2375,10 +2369,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -2386,10 +2380,10 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
@@ -2400,7 +2394,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12">
@@ -2408,10 +2402,10 @@
         <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13">
@@ -2419,10 +2413,10 @@
         <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14">
@@ -2430,10 +2424,10 @@
         <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15">
@@ -2441,10 +2435,10 @@
         <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16">
@@ -2452,7 +2446,7 @@
         <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C16" t="s">
         <v>86</v>
@@ -2485,10 +2479,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3">
@@ -2499,7 +2493,7 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4">
@@ -2507,10 +2501,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5">
@@ -2521,7 +2515,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6">
@@ -2532,7 +2526,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7">
@@ -2540,10 +2534,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8">
@@ -2554,7 +2548,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2556,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -2576,7 +2570,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -2587,7 +2581,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12">
@@ -2598,7 +2592,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -2606,10 +2600,10 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14">
@@ -2617,10 +2611,10 @@
         <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C14" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15">
@@ -2628,10 +2622,10 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16">
@@ -2639,10 +2633,10 @@
         <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C16" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2647,7 @@
         <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -2683,10 +2677,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3">
@@ -2694,10 +2688,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4">
@@ -2708,7 +2702,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
@@ -2719,7 +2713,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6">
@@ -2727,10 +2721,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7">
@@ -2741,7 +2735,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -2749,10 +2743,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2763,7 +2757,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2774,7 +2768,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11">
@@ -2782,10 +2776,10 @@
         <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
@@ -2793,10 +2787,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13">
@@ -2804,10 +2798,10 @@
         <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C13" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14">
@@ -2815,10 +2809,10 @@
         <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C14" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15">
@@ -2826,10 +2820,10 @@
         <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2859,10 +2853,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -2870,10 +2864,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4">
@@ -2881,10 +2875,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5">
@@ -2895,7 +2889,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
@@ -2906,7 +2900,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
@@ -2914,10 +2908,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8">
@@ -2925,10 +2919,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2936,10 +2930,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -2947,10 +2941,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -2961,7 +2955,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12">
@@ -2969,10 +2963,10 @@
         <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -2983,7 +2977,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
@@ -2991,10 +2985,10 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15">
@@ -3005,7 +2999,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
@@ -3013,10 +3007,10 @@
         <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17">
@@ -3024,10 +3018,10 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C17" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18">
@@ -3035,10 +3029,10 @@
         <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C18" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19">
@@ -3046,10 +3040,10 @@
         <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -3835,43 +3829,43 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>140</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>141</v>
-      </c>
-      <c r="C5" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" t="s">
         <v>141</v>
-      </c>
-      <c r="C6" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
         <v>144</v>
@@ -3879,156 +3873,145 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
         <v>141</v>
-      </c>
-      <c r="C14" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C21" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" t="s">
         <v>164</v>
-      </c>
-      <c r="C22" t="s">
-        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4058,10 +4041,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" t="s">
         <v>166</v>
-      </c>
-      <c r="C2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -4069,10 +4052,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
         <v>168</v>
-      </c>
-      <c r="C3" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -4080,10 +4063,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" t="s">
         <v>170</v>
-      </c>
-      <c r="C4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="5">
@@ -4094,7 +4077,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
@@ -4102,10 +4085,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7">
@@ -4116,7 +4099,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -4124,10 +4107,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
@@ -4135,10 +4118,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -4146,10 +4129,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -4157,10 +4140,10 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -4171,7 +4154,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -4179,10 +4162,10 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" t="s">
         <v>178</v>
-      </c>
-      <c r="C13" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="14">
@@ -4193,7 +4176,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
@@ -4201,10 +4184,10 @@
         <v>47</v>
       </c>
       <c r="B15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" t="s">
         <v>180</v>
-      </c>
-      <c r="C15" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="16">
@@ -4212,10 +4195,10 @@
         <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17">
@@ -4223,10 +4206,10 @@
         <v>53</v>
       </c>
       <c r="B17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" t="s">
         <v>182</v>
-      </c>
-      <c r="C17" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="18">
@@ -4234,7 +4217,7 @@
         <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C18" t="s">
         <v>110</v>
@@ -4267,10 +4250,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" t="s">
         <v>185</v>
-      </c>
-      <c r="C2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="3">
@@ -4278,10 +4261,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" t="s">
         <v>187</v>
-      </c>
-      <c r="C3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="4">
@@ -4289,10 +4272,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
@@ -4300,10 +4283,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" t="s">
         <v>190</v>
-      </c>
-      <c r="C5" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="6">
@@ -4314,7 +4297,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
@@ -4322,10 +4305,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
@@ -4333,10 +4316,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
@@ -4344,10 +4327,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -4355,10 +4338,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" t="s">
         <v>195</v>
-      </c>
-      <c r="C10" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -4366,10 +4349,10 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -4377,10 +4360,10 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" t="s">
         <v>197</v>
-      </c>
-      <c r="C12" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -4388,10 +4371,10 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14">
@@ -4399,10 +4382,10 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
@@ -4410,10 +4393,10 @@
         <v>47</v>
       </c>
       <c r="B15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" t="s">
         <v>200</v>
-      </c>
-      <c r="C15" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="16">
@@ -4421,10 +4404,10 @@
         <v>50</v>
       </c>
       <c r="B16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" t="s">
         <v>202</v>
-      </c>
-      <c r="C16" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="17">
@@ -4432,10 +4415,10 @@
         <v>53</v>
       </c>
       <c r="B17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" t="s">
         <v>204</v>
-      </c>
-      <c r="C17" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="18">
@@ -4443,10 +4426,10 @@
         <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -4476,10 +4459,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" t="s">
         <v>207</v>
-      </c>
-      <c r="C2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="3">
@@ -4487,10 +4470,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4">
@@ -4498,10 +4481,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5">
@@ -4512,7 +4495,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -4523,7 +4506,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7">
@@ -4531,10 +4514,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
@@ -4542,10 +4525,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
@@ -4556,7 +4539,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -4564,10 +4547,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" t="s">
         <v>216</v>
-      </c>
-      <c r="C10" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -4575,10 +4558,10 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -4589,7 +4572,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13">
@@ -4600,7 +4583,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14">
@@ -4608,10 +4591,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
@@ -4619,10 +4602,10 @@
         <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16">
@@ -4630,10 +4613,10 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17">
@@ -4641,10 +4624,10 @@
         <v>47</v>
       </c>
       <c r="B17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" t="s">
         <v>219</v>
-      </c>
-      <c r="C17" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="18">
@@ -4652,10 +4635,10 @@
         <v>50</v>
       </c>
       <c r="B18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" t="s">
         <v>221</v>
-      </c>
-      <c r="C18" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="19">
@@ -4663,10 +4646,10 @@
         <v>53</v>
       </c>
       <c r="B19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" t="s">
         <v>223</v>
-      </c>
-      <c r="C19" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="20">
@@ -4677,7 +4660,7 @@
         <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4707,10 +4690,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" t="s">
         <v>226</v>
-      </c>
-      <c r="C2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="3">
@@ -4718,10 +4701,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" t="s">
         <v>228</v>
-      </c>
-      <c r="C3" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="4">
@@ -4729,59 +4712,59 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C8" t="s">
         <v>234</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>235</v>
@@ -4792,7 +4775,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>237</v>
@@ -4803,79 +4786,79 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" t="s">
         <v>239</v>
-      </c>
-      <c r="C11" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>237</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>239</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
         <v>244</v>
-      </c>
-      <c r="C17" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="18">
@@ -4886,15 +4869,15 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
         <v>247</v>
@@ -4902,46 +4885,35 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" t="s">
         <v>248</v>
-      </c>
-      <c r="C20" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
+++ b/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
@@ -494,7 +494,7 @@
     <t xml:space="preserve">22 (44%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Other/Unknown Ancestry</t>
+    <t xml:space="preserve">Unknown/Mixed Ancestry</t>
   </si>
   <si>
     <t xml:space="preserve">4 (15.4%)</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">5 (83.3%)</t>
   </si>
   <si>
+    <t xml:space="preserve">2 (4.3%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">12 (25.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (4.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">7.07</t>
@@ -4852,7 +4852,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -4863,7 +4863,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>

--- a/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
+++ b/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
@@ -440,15 +440,15 @@
     <t xml:space="preserve">12 (46.2%)</t>
   </si>
   <si>
+    <t xml:space="preserve">24 (48%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (53.8%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">26 (52%)</t>
   </si>
   <si>
-    <t xml:space="preserve">14 (53.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (48%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 (3.8%)</t>
   </si>
   <si>
@@ -713,52 +713,52 @@
     <t xml:space="preserve">3 (50%)</t>
   </si>
   <si>
-    <t xml:space="preserve">29 (61.7%)</t>
+    <t xml:space="preserve">28 (59.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (40.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (12.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (66.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 (48.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (16.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (21.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (19.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (23.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (6.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (83.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">18 (38.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (12.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (33.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (66.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (48.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (21.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 (59.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (19.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (23.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (6.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (83.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">2 (4.3%)</t>
@@ -3967,7 +3967,7 @@
         <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18">
@@ -4792,7 +4792,7 @@
         <v>235</v>
       </c>
       <c r="C11" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12">
@@ -4803,7 +4803,7 @@
         <v>237</v>
       </c>
       <c r="C12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13">
@@ -4825,7 +4825,7 @@
         <v>237</v>
       </c>
       <c r="C14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -4836,7 +4836,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16">
@@ -4844,10 +4844,10 @@
         <v>41</v>
       </c>
       <c r="B16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" t="s">
         <v>243</v>
-      </c>
-      <c r="C16" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="17">

--- a/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
+++ b/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="348">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -41,28 +41,28 @@
     <t xml:space="preserve">Number Cohort</t>
   </si>
   <si>
-    <t xml:space="preserve">45 (20.36%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176 (79.64%)</t>
+    <t xml:space="preserve">47 (21.27%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174 (78.73%)</t>
   </si>
   <si>
     <t xml:space="preserve">Female</t>
   </si>
   <si>
-    <t xml:space="preserve">25 (55.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77 (43.8%)</t>
+    <t xml:space="preserve">26 (55.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76 (43.7%)</t>
   </si>
   <si>
     <t xml:space="preserve">Male</t>
   </si>
   <si>
-    <t xml:space="preserve">20 (44.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99 (56.2%)</t>
+    <t xml:space="preserve">21 (44.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98 (56.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">American Indian or Alaska Native</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Black or African American</t>
   </si>
   <si>
-    <t xml:space="preserve">5 (11.1%)</t>
+    <t xml:space="preserve">5 (10.6%)</t>
   </si>
   <si>
     <t xml:space="preserve">14 (8%)</t>
@@ -98,985 +98,955 @@
     <t xml:space="preserve">Other/Unknown Race</t>
   </si>
   <si>
-    <t xml:space="preserve">7 (15.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 (11.9%)</t>
+    <t xml:space="preserve">8 (17%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (11.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">White</t>
   </si>
   <si>
-    <t xml:space="preserve">33 (73.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135 (76.7%)</t>
+    <t xml:space="preserve">34 (72.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134 (77%)</t>
   </si>
   <si>
     <t xml:space="preserve">Hispanic or Latino</t>
   </si>
   <si>
-    <t xml:space="preserve">4 (8.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (8.5%)</t>
+    <t xml:space="preserve">6 (12.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (7.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">Not Hispanic or Latino</t>
   </si>
   <si>
-    <t xml:space="preserve">39 (86.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160 (90.9%)</t>
+    <t xml:space="preserve">39 (83%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 (92%)</t>
   </si>
   <si>
     <t xml:space="preserve">Other/Unknown Ethnicity</t>
   </si>
   <si>
+    <t xml:space="preserve">2 (4.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (8.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (9.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (14.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 (74.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136 (78.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (2.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_os_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_efs_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_tmb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 (29.17%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68 (70.83%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (46.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (35.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (53.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 (64.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (1.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (3.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (2.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (8.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 (75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 (72.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (7.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (85.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 (88.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (4.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (13.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (5.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 (69.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (13.92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68 (86.08%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (9.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (90.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (81.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 (73.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63 (92.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (18.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (72.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56 (82.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (15.49%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 (84.51%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (45.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 (41.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (54.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 (58.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (6.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (18.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41 (68.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (13.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 (81.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (15%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (8.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 (70%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 (34.21%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 (65.79%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (42.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (15.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (48%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (3.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA (NA%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (30.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (14%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (57.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39 (78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (23.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 (69.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 (84%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (7.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (26.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 (44%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;NA&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (10.26%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 (89.74%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (42.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (57.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (11.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 (71.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (8.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 (91.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (68.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (29.63%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (70.37%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (52.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (47.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (12.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (31.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (5.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (37.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (10.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (89.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (36.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (15.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (68%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (29.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (70.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (23.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (5.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (52.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (87.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (88.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (58.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (15.09%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 (84.91%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (62.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 (40%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (31.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (28.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (13.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (35.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 (46.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (22.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 (57.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (24.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (6.7%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 (4.4%)</t>
   </si>
   <si>
-    <t xml:space="preserve">AFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (9.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (9.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 (77.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136 (77.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (2.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_os_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_efs_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_tmb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 (28.12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69 (71.88%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (44.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 (36.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (55.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 (63.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (1.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (3.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (2.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (8.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (14.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (11.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (74.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 (72.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (7.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (85.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61 (88.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (4.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (5.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48 (69.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68</t>
+    <t xml:space="preserve">12 (26.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (26.32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (73.68%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (35.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (40%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (64.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (28.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (80%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (71.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (7.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (21.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (92.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (73.33%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (26.67%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (36.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (28.57%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (71.43%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (15%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (65%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (70%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (30.77%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (69.23%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (88.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (55.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (22.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (66.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81</t>
   </si>
   <si>
     <t xml:space="preserve">0.39</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (13.92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68 (86.08%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (9.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (90.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (4.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (8.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (1.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (81.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 (73.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63 (92.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (18.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (7.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (72.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56 (82.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (15.49%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 (84.51%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (45.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 (41.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (54.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 (58.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (6.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (18.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41 (68.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (13.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49 (81.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (8.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 (34.21%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 (65.79%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (46.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (48%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (53.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (3.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA (NA%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (30.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (57.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39 (78%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (23.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 (69.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 (84%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (7.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (26.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 (44%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown/Mixed Ancestry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (15.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (10.26%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 (89.74%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (42.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (57.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (11.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 (71.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (8.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 (91.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (68.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (29.63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (70.37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (52.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (47.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (12.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (31.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (5.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (37.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (10.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (89.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (36.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (15.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (29.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (70.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (23.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (5.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (17.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (52.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (11.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (87.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (88.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (58.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (11.32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 (88.68%)</t>
+    <t xml:space="preserve">4 (44.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (77.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (22.22%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (77.78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (85.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (78.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (24%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (76%)</t>
   </si>
   <si>
     <t xml:space="preserve">3 (50%)</t>
   </si>
   <si>
-    <t xml:space="preserve">28 (59.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (40.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (12.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
+    <t xml:space="preserve">8 (42.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (57.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (73.7%)</t>
   </si>
   <si>
     <t xml:space="preserve">2 (33.3%)</t>
   </si>
   <si>
-    <t xml:space="preserve">16 (34%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 (66.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (48.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (21.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (19.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (23.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (6.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (83.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 (38.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (4.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (25.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (26.32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (73.68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (35.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (64.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (28.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (71.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (7.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (21.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (92.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (73.33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (26.67%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (36.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (28.57%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (71.43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (62.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (65%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (30.77%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (69.23%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (11.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (88.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (33.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (55.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (22.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (66.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (23.08%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (76.92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (22.22%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (77.78%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (85.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (78.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (24%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (76%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (42.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (57.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (73.7%)</t>
   </si>
   <si>
     <t xml:space="preserve">4 (21.1%)</t>
@@ -1577,26 +1547,26 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1607,68 +1577,68 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1698,10 +1668,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -1709,10 +1679,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -1720,10 +1690,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -1731,10 +1701,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
@@ -1742,10 +1712,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
@@ -1756,7 +1726,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8">
@@ -1764,10 +1734,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9">
@@ -1778,95 +1748,95 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C14" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C15" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1896,10 +1866,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3">
@@ -1907,10 +1877,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4">
@@ -1918,10 +1888,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
@@ -1929,10 +1899,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6">
@@ -1940,10 +1910,10 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
@@ -1951,10 +1921,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
@@ -1965,7 +1935,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9">
@@ -1973,10 +1943,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -1984,10 +1954,10 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -1995,76 +1965,76 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C17" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -2094,10 +2064,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3">
@@ -2105,10 +2075,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4">
@@ -2116,10 +2086,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
@@ -2130,7 +2100,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
@@ -2141,7 +2111,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
@@ -2149,10 +2119,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8">
@@ -2163,7 +2133,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
@@ -2171,10 +2141,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2185,7 +2155,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11">
@@ -2193,76 +2163,76 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C15" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C16" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2292,10 +2262,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -2303,10 +2273,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4">
@@ -2314,10 +2284,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
@@ -2328,7 +2298,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6">
@@ -2339,7 +2309,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7">
@@ -2347,10 +2317,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
@@ -2361,7 +2331,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -2369,87 +2339,87 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C9" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C12" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C13" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -2479,10 +2449,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -2493,7 +2463,7 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4">
@@ -2501,10 +2471,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C4" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5">
@@ -2515,7 +2485,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
@@ -2526,7 +2496,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7">
@@ -2534,10 +2504,10 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
@@ -2548,7 +2518,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -2556,10 +2526,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C9" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -2570,7 +2540,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11">
@@ -2581,73 +2551,73 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C14" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="C15" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -2677,10 +2647,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
@@ -2688,10 +2658,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4">
@@ -2702,7 +2672,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5">
@@ -2713,7 +2683,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6">
@@ -2721,10 +2691,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7">
@@ -2735,7 +2705,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8">
@@ -2743,10 +2713,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -2757,73 +2727,73 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C11" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C12" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C13" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C14" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2853,10 +2823,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3">
@@ -2864,10 +2834,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="C3" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4">
@@ -2875,10 +2845,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="C4" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5">
@@ -2889,7 +2859,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
@@ -2900,7 +2870,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
@@ -2908,10 +2878,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="C7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -2919,10 +2889,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2930,10 +2900,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -2941,10 +2911,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>339</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -2955,95 +2925,95 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="C12" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="C14" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C16" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C17" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C18" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C19" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -3073,10 +3043,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -3084,10 +3054,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -3095,10 +3065,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
@@ -3109,7 +3079,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -3117,10 +3087,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -3128,10 +3098,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -3139,10 +3109,10 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -3150,10 +3120,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -3161,10 +3131,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -3172,10 +3142,10 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -3183,10 +3153,10 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -3197,7 +3167,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -3205,98 +3175,98 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3326,10 +3296,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -3337,10 +3307,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -3348,10 +3318,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
         <v>92</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -3362,7 +3332,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -3373,7 +3343,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -3381,10 +3351,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -3395,7 +3365,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -3403,10 +3373,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -3414,10 +3384,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -3428,7 +3398,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
@@ -3436,10 +3406,10 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3450,7 +3420,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -3458,98 +3428,98 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3579,10 +3549,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3">
@@ -3590,10 +3560,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -3601,10 +3571,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5">
@@ -3615,7 +3585,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -3626,7 +3596,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -3634,10 +3604,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
@@ -3645,10 +3615,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
@@ -3656,10 +3626,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -3667,10 +3637,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -3681,7 +3651,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
@@ -3689,87 +3659,87 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3799,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
@@ -3810,10 +3780,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
@@ -3821,131 +3791,131 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="s">
         <v>140</v>
-      </c>
-      <c r="C6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" t="s">
         <v>140</v>
-      </c>
-      <c r="C7" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" t="s">
         <v>140</v>
-      </c>
-      <c r="C15" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="16">
@@ -3953,65 +3923,76 @@
         <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>155</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
-        <v>164</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4041,10 +4022,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -4052,10 +4033,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4">
@@ -4063,10 +4044,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5">
@@ -4077,7 +4058,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
@@ -4085,10 +4066,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
@@ -4099,7 +4080,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
@@ -4107,10 +4088,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9">
@@ -4118,10 +4099,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -4129,10 +4110,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -4140,87 +4121,87 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -4250,10 +4231,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3">
@@ -4261,10 +4242,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4">
@@ -4272,10 +4253,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" t="s">
         <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="5">
@@ -4283,10 +4264,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
@@ -4297,7 +4278,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
@@ -4305,10 +4286,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
@@ -4316,10 +4297,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9">
@@ -4327,10 +4308,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -4338,10 +4319,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -4349,10 +4330,10 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -4360,76 +4341,76 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4459,10 +4440,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
@@ -4470,10 +4451,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4">
@@ -4481,10 +4462,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
@@ -4495,7 +4476,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6">
@@ -4506,7 +4487,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -4514,10 +4495,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8">
@@ -4525,10 +4506,10 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
@@ -4539,7 +4520,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -4547,10 +4528,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -4558,10 +4539,10 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -4572,95 +4553,95 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C16" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4690,10 +4671,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3">
@@ -4701,10 +4682,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
@@ -4712,131 +4693,131 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>230</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16">
@@ -4844,76 +4825,87 @@
         <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>242</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>213</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="C20" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c r="C21" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C22" t="s">
-        <v>250</v>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
+++ b/analyses/demo-clin-stats/results/demo-clin-stats-by-histology.xlsx
@@ -27,27 +27,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
+  <si>
+    <t xml:space="preserve">Term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPG P/LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No CPG P/LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number Cohort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 (21.27%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174 (78.73%)</t>
+  </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">CPG P/LP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No CPG P/LP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number Cohort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 (21.27%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174 (78.73%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female</t>
+    <t xml:space="preserve">Predicted sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Female</t>
   </si>
   <si>
     <t xml:space="preserve">26 (55.3%)</t>
@@ -56,7 +68,7 @@
     <t xml:space="preserve">76 (43.7%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Male</t>
+    <t xml:space="preserve">     Male</t>
   </si>
   <si>
     <t xml:space="preserve">21 (44.7%)</t>
@@ -65,7 +77,13 @@
     <t xml:space="preserve">98 (56.3%)</t>
   </si>
   <si>
-    <t xml:space="preserve">American Indian or Alaska Native</t>
+    <t xml:space="preserve">Race</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     American Indian or Alaska Native</t>
   </si>
   <si>
     <t xml:space="preserve">0 (0%)</t>
@@ -74,13 +92,13 @@
     <t xml:space="preserve">2 (1.1%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Asian</t>
+    <t xml:space="preserve">     Asian</t>
   </si>
   <si>
     <t xml:space="preserve">3 (1.7%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Black or African American</t>
+    <t xml:space="preserve">     Black or African American</t>
   </si>
   <si>
     <t xml:space="preserve">5 (10.6%)</t>
@@ -89,13 +107,13 @@
     <t xml:space="preserve">14 (8%)</t>
   </si>
   <si>
-    <t xml:space="preserve">More Than One Race</t>
+    <t xml:space="preserve">     More Than One Race</t>
   </si>
   <si>
     <t xml:space="preserve">1 (0.6%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Other/Unknown Race</t>
+    <t xml:space="preserve">     Other/Unknown Race</t>
   </si>
   <si>
     <t xml:space="preserve">8 (17%)</t>
@@ -104,7 +122,7 @@
     <t xml:space="preserve">20 (11.5%)</t>
   </si>
   <si>
-    <t xml:space="preserve">White</t>
+    <t xml:space="preserve">     White</t>
   </si>
   <si>
     <t xml:space="preserve">34 (72.3%)</t>
@@ -113,7 +131,13 @@
     <t xml:space="preserve">134 (77%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hispanic or Latino</t>
+    <t xml:space="preserve">Ethnicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Hispanic or Latino</t>
   </si>
   <si>
     <t xml:space="preserve">6 (12.8%)</t>
@@ -122,7 +146,7 @@
     <t xml:space="preserve">13 (7.5%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Hispanic or Latino</t>
+    <t xml:space="preserve">     Not Hispanic or Latino</t>
   </si>
   <si>
     <t xml:space="preserve">39 (83%)</t>
@@ -131,13 +155,19 @@
     <t xml:space="preserve">160 (92%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Other/Unknown Ethnicity</t>
+    <t xml:space="preserve">     Other/Unknown Ethnicity</t>
   </si>
   <si>
     <t xml:space="preserve">2 (4.3%)</t>
   </si>
   <si>
-    <t xml:space="preserve">AFR</t>
+    <t xml:space="preserve">Genetic Ancestry Superpopulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     AFR</t>
   </si>
   <si>
     <t xml:space="preserve">4 (8.5%)</t>
@@ -146,16 +176,16 @@
     <t xml:space="preserve">17 (9.8%)</t>
   </si>
   <si>
-    <t xml:space="preserve">AMR</t>
+    <t xml:space="preserve">     AMR</t>
   </si>
   <si>
     <t xml:space="preserve">7 (14.9%)</t>
   </si>
   <si>
-    <t xml:space="preserve">EAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR</t>
+    <t xml:space="preserve">     EAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     EUR</t>
   </si>
   <si>
     <t xml:space="preserve">35 (74.5%)</t>
@@ -164,7 +194,7 @@
     <t xml:space="preserve">136 (78.2%)</t>
   </si>
   <si>
-    <t xml:space="preserve">SAS</t>
+    <t xml:space="preserve">     SAS</t>
   </si>
   <si>
     <t xml:space="preserve">1 (2.1%)</t>
@@ -173,7 +203,7 @@
     <t xml:space="preserve">4 (2.3%)</t>
   </si>
   <si>
-    <t xml:space="preserve">median_age</t>
+    <t xml:space="preserve">Median age at diagnosis, years</t>
   </si>
   <si>
     <t xml:space="preserve">6.12</t>
@@ -182,25 +212,10 @@
     <t xml:space="preserve">9.24</t>
   </si>
   <si>
-    <t xml:space="preserve">median_os_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_efs_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_tmb</t>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median tumor mutation burden</t>
   </si>
   <si>
     <t xml:space="preserve">0.31</t>
@@ -209,12 +224,18 @@
     <t xml:space="preserve">0.28</t>
   </si>
   <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
     <t xml:space="preserve">28 (29.17%)</t>
   </si>
   <si>
     <t xml:space="preserve">68 (70.83%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
     <t xml:space="preserve">13 (46.4%)</t>
   </si>
   <si>
@@ -227,6 +248,9 @@
     <t xml:space="preserve">44 (64.7%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.36</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 (1.5%)</t>
   </si>
   <si>
@@ -251,6 +275,9 @@
     <t xml:space="preserve">49 (72.1%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 (7.4%)</t>
   </si>
   <si>
@@ -263,6 +290,9 @@
     <t xml:space="preserve">3 (4.4%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.95</t>
+  </si>
+  <si>
     <t xml:space="preserve">9 (13.2%)</t>
   </si>
   <si>
@@ -278,16 +308,7 @@
     <t xml:space="preserve">8.64</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78</t>
+    <t xml:space="preserve">0.41</t>
   </si>
   <si>
     <t xml:space="preserve">0.4</t>
@@ -296,12 +317,18 @@
     <t xml:space="preserve">0.58</t>
   </si>
   <si>
+    <t xml:space="preserve">0.01</t>
+  </si>
+  <si>
     <t xml:space="preserve">11 (13.92%)</t>
   </si>
   <si>
     <t xml:space="preserve">68 (86.08%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.69</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 (9.1%)</t>
   </si>
   <si>
@@ -311,18 +338,27 @@
     <t xml:space="preserve">10 (90.9%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.02</t>
+  </si>
+  <si>
     <t xml:space="preserve">9 (81.8%)</t>
   </si>
   <si>
     <t xml:space="preserve">50 (73.5%)</t>
   </si>
   <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
     <t xml:space="preserve">11 (100%)</t>
   </si>
   <si>
     <t xml:space="preserve">63 (92.6%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 (18.2%)</t>
   </si>
   <si>
@@ -338,27 +374,21 @@
     <t xml:space="preserve">9.74</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.17</t>
   </si>
   <si>
+    <t xml:space="preserve">0.47</t>
+  </si>
+  <si>
     <t xml:space="preserve">11 (15.49%)</t>
   </si>
   <si>
     <t xml:space="preserve">60 (84.51%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.18</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 (45.5%)</t>
   </si>
   <si>
@@ -389,6 +419,9 @@
     <t xml:space="preserve">3 (5%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.51</t>
+  </si>
+  <si>
     <t xml:space="preserve">9 (15%)</t>
   </si>
   <si>
@@ -404,24 +437,15 @@
     <t xml:space="preserve">4.56</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.33</t>
   </si>
   <si>
     <t xml:space="preserve">0.29</t>
   </si>
   <si>
+    <t xml:space="preserve">0.23</t>
+  </si>
+  <si>
     <t xml:space="preserve">26 (34.21%)</t>
   </si>
   <si>
@@ -437,7 +461,7 @@
     <t xml:space="preserve">16 (32%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
+    <t xml:space="preserve">     Unknown</t>
   </si>
   <si>
     <t xml:space="preserve">4 (15.4%)</t>
@@ -446,6 +470,9 @@
     <t xml:space="preserve">24 (48%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.56</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 (3.8%)</t>
   </si>
   <si>
@@ -467,6 +494,9 @@
     <t xml:space="preserve">39 (78%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 (23.1%)</t>
   </si>
   <si>
@@ -482,6 +512,9 @@
     <t xml:space="preserve">2 (7.7%)</t>
   </si>
   <si>
+    <t xml:space="preserve">1.90e-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">7 (26.9%)</t>
   </si>
   <si>
@@ -491,7 +524,7 @@
     <t xml:space="preserve">22 (44%)</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;NA&gt;</t>
+    <t xml:space="preserve">     Unknown Ancestry</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
@@ -500,108 +533,111 @@
     <t xml:space="preserve">9.45</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34</t>
+    <t xml:space="preserve">1.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (10.26%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 (89.74%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (42.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (57.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (11.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 (71.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (8.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 (91.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (68.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (29.63%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (70.37%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (52.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (47.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (12.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (31.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (5.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (37.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">0.71</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (10.26%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 (89.74%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (42.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (57.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (11.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 (71.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (8.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 (91.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (68.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (29.63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (70.37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (52.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (47.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (12.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (31.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (5.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (37.5%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 (10.5%)</t>
   </si>
   <si>
@@ -611,6 +647,9 @@
     <t xml:space="preserve">17 (89.5%)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.49</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 (25%)</t>
   </si>
   <si>
@@ -626,429 +665,387 @@
     <t xml:space="preserve">2.26</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84</t>
+    <t xml:space="preserve">0.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (68%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (29.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (70.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (23.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (5.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (52.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (87.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (88.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (58.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (15.09%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 (84.91%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (62.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 (40%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (31.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (28.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (13.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (2.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Native Hawaiian or Other Pacific Islander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (35.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 (46.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (22.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 (57.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (24.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (6.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (4.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (26.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (26.32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (73.68%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (35.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (40%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (64.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (28.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (80%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (71.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (7.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (21.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (92.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (73.33%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (26.67%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (36.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (28.57%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (71.43%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (15%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (65%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (70%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (30.77%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (69.23%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (88.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (55.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (22.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (66.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (44.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (77.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.23</t>
   </si>
   <si>
     <t xml:space="preserve">0.38</t>
   </si>
   <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (22.22%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (77.78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (85.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (78.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (24%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (76%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (42.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (57.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (73.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (66.7%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.72</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (29.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (70.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (23.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (5.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (17.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (52.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (11.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (87.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (88.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (58.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (15.09%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 (84.91%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (62.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (31.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (28.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (13.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (2.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native Hawaiian or Other Pacific Islander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (35.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 (46.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (22.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 (57.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (24.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (6.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (4.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (26.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (26.32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (73.68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (35.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (64.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (28.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (71.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (7.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (21.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (92.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (73.33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (26.67%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (36.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (28.57%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (71.43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (65%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (30.77%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (69.23%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (11.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (88.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (33.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (55.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (22.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (66.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (44.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (77.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (22.22%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (77.78%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (85.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (78.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (24%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (76%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (42.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (57.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (73.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (33.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (66.7%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 (21.1%)</t>
   </si>
   <si>
@@ -1061,16 +1058,7 @@
     <t xml:space="preserve">10.03</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42</t>
+    <t xml:space="preserve">0.91</t>
   </si>
 </sst>
 </file>
@@ -1409,104 +1397,134 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1519,6 +1537,9 @@
       <c r="C11" t="s">
         <v>30</v>
       </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1530,16 +1551,22 @@
       <c r="C12" t="s">
         <v>33</v>
       </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -1552,6 +1579,9 @@
       <c r="C14" t="s">
         <v>38</v>
       </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -1561,51 +1591,66 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1613,32 +1658,69 @@
         <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
         <v>54</v>
       </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
+      <c r="D21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
         <v>57</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>58</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
         <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1662,60 +1744,78 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>260</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>249</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>262</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>264</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="7">
@@ -1723,10 +1823,13 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>267</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1734,10 +1837,13 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>269</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1745,32 +1851,41 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>258</v>
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>270</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>269</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1778,32 +1893,41 @@
         <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>272</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>252</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>270</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1811,32 +1935,69 @@
         <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
-        <v>263</v>
+        <v>150</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>274</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>150</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1860,71 +2021,92 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>280</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>186</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>268</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>186</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>150</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1932,10 +2114,13 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>174</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1943,10 +2128,13 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>176</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1954,10 +2142,13 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="11">
@@ -1965,10 +2156,13 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>268</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>174</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1976,10 +2170,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>176</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1987,54 +2184,97 @@
         <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>150</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>150</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>274</v>
+        <v>174</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>276</v>
+        <v>176</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C18" t="s">
+        <v>284</v>
+      </c>
+      <c r="D18" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>285</v>
+      </c>
+      <c r="D19" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2058,71 +2298,92 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>287</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>279</v>
+        <v>288</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="C5" t="s">
-        <v>280</v>
+        <v>288</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>281</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>289</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2130,10 +2391,13 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2141,10 +2405,13 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C9" t="s">
-        <v>285</v>
+        <v>292</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2152,10 +2419,13 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>280</v>
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -2163,10 +2433,13 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>286</v>
+        <v>293</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2174,10 +2447,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>291</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>294</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2185,54 +2461,97 @@
         <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>287</v>
+        <v>289</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>289</v>
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
-        <v>291</v>
+        <v>295</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>292</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>296</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" t="s">
+        <v>298</v>
+      </c>
+      <c r="D18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2256,71 +2575,92 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>302</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>297</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>303</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>297</v>
+        <v>304</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>299</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>301</v>
+        <v>303</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2328,10 +2668,13 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>297</v>
+        <v>305</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2339,87 +2682,139 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C9" t="s">
-        <v>298</v>
+        <v>307</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>297</v>
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>302</v>
+        <v>303</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>306</v>
       </c>
       <c r="C12" t="s">
-        <v>303</v>
+        <v>304</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>304</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>305</v>
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>306</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
-        <v>307</v>
+        <v>303</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>308</v>
       </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" t="s">
         <v>309</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
         <v>310</v>
+      </c>
+      <c r="C17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>312</v>
+      </c>
+      <c r="C18" t="s">
+        <v>232</v>
+      </c>
+      <c r="D18" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -2443,71 +2838,92 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>302</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>301</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>307</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>306</v>
       </c>
       <c r="C5" t="s">
-        <v>302</v>
+        <v>314</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>297</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>303</v>
+        <v>308</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2515,10 +2931,13 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>297</v>
+        <v>303</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2526,10 +2945,13 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>309</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2537,10 +2959,13 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>297</v>
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="11">
@@ -2548,10 +2973,13 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>302</v>
+        <v>303</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2559,10 +2987,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>306</v>
       </c>
       <c r="C12" t="s">
-        <v>302</v>
+        <v>317</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2570,54 +3001,97 @@
         <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>300</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>301</v>
+        <v>303</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>313</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>314</v>
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>316</v>
+        <v>308</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>318</v>
+        <v>308</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="C17" t="s">
+        <v>307</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>318</v>
+      </c>
+      <c r="C18" t="s">
         <v>319</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>320</v>
+      </c>
+      <c r="C19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D19" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -2641,60 +3115,78 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C2" t="s">
-        <v>321</v>
+        <v>323</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>306</v>
       </c>
       <c r="C4" t="s">
-        <v>322</v>
+        <v>324</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>324</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="7">
@@ -2702,10 +3194,13 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>325</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2713,10 +3208,13 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>326</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2724,76 +3222,125 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>323</v>
+        <v>325</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C11" t="s">
-        <v>324</v>
+        <v>327</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>327</v>
+        <v>270</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>328</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>329</v>
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>325</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>326</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" t="s">
+        <v>329</v>
+      </c>
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -2817,82 +3364,106 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>333</v>
+        <v>331</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>334</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>335</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C4" t="s">
-        <v>336</v>
+        <v>333</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>334</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>203</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>337</v>
+        <v>200</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2900,10 +3471,13 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>203</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2911,76 +3485,97 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>335</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C12" t="s">
-        <v>340</v>
+        <v>203</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>337</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>205</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>334</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>341</v>
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>339</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -2988,32 +3583,69 @@
         <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>345</v>
+        <v>200</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C18" t="s">
-        <v>347</v>
+        <v>340</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>319</v>
+        <v>200</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -3037,104 +3669,134 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3142,10 +3804,13 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3153,10 +3818,13 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3164,10 +3832,13 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="14">
@@ -3175,10 +3846,13 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3186,54 +3860,69 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>88</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -3241,32 +3930,69 @@
         <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>89</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3290,104 +4016,134 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3395,10 +4151,13 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3406,10 +4165,13 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>105</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3417,10 +4179,13 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -3428,10 +4193,13 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3439,54 +4207,69 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>108</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -3494,32 +4277,69 @@
         <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>86</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3543,82 +4363,106 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>118</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>121</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>123</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>124</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>124</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3626,10 +4470,13 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>125</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3637,10 +4484,13 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3648,10 +4498,13 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -3659,10 +4512,13 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>127</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3670,76 +4526,125 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>128</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>129</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
         <v>124</v>
       </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3763,104 +4668,134 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>142</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>143</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>149</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>149</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>150</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3868,10 +4803,13 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>152</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3879,10 +4817,13 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3890,10 +4831,13 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -3901,10 +4845,13 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>157</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3912,54 +4859,69 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>159</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>157</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>149</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>149</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -3967,32 +4929,69 @@
         <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>150</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C21" t="s">
-        <v>160</v>
+        <v>164</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C22" t="s">
-        <v>162</v>
+        <v>146</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4016,82 +5015,106 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>172</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>175</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>177</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>178</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>179</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -4099,10 +5122,13 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>180</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -4110,98 +5136,153 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>181</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>183</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
-        <v>176</v>
+        <v>184</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>180</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>179</v>
+        <v>180</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C17" t="s">
-        <v>180</v>
+        <v>187</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>178</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -4225,82 +5306,106 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>193</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>196</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>197</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>199</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>200</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -4308,10 +5413,13 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>199</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -4319,10 +5427,13 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>199</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +5441,13 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -4341,10 +5455,13 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>203</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -4352,10 +5469,13 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>196</v>
+        <v>205</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -4363,54 +5483,97 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>150</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>208</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
         <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>209</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>197</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4434,82 +5597,106 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>217</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>218</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>211</v>
+        <v>221</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -4517,10 +5704,13 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>222</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -4528,10 +5718,13 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>223</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -4539,10 +5732,13 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="12">
@@ -4550,10 +5746,13 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>225</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -4561,54 +5760,69 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>227</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>215</v>
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>209</v>
+        <v>220</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>217</v>
+        <v>225</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -4616,32 +5830,69 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>150</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>229</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>221</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -4665,104 +5916,134 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>235</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>225</v>
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>226</v>
+        <v>237</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="C5" t="s">
-        <v>227</v>
+        <v>238</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>239</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>229</v>
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>229</v>
+        <v>240</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>231</v>
+        <v>241</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>232</v>
+        <v>241</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -4770,10 +6051,13 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C11" t="s">
-        <v>233</v>
+        <v>243</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -4781,10 +6065,13 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>234</v>
+        <v>244</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -4792,10 +6079,13 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>235</v>
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="14">
@@ -4803,10 +6093,13 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>246</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -4814,98 +6107,153 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C15" t="s">
-        <v>236</v>
+        <v>247</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>248</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>213</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>231</v>
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>238</v>
+        <v>241</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>239</v>
+        <v>250</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>240</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>241</v>
+        <v>251</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
         <v>243</v>
       </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>201</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>244</v>
+        <v>252</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>245</v>
+        <v>253</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" t="s">
+        <v>257</v>
+      </c>
+      <c r="D25" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
